--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -2755,10 +2755,10 @@
         <v>3200</v>
       </c>
       <c r="F41" s="3">
-        <v>237500</v>
+        <v>228100</v>
       </c>
       <c r="G41" s="3">
-        <v>237500</v>
+        <v>228100</v>
       </c>
       <c r="H41" s="3">
         <v>279200</v>
@@ -2826,10 +2826,10 @@
         <v>2200</v>
       </c>
       <c r="F42" s="3">
-        <v>200</v>
+        <v>9600</v>
       </c>
       <c r="G42" s="3">
-        <v>200</v>
+        <v>9600</v>
       </c>
       <c r="H42" s="3">
         <v>300</v>
@@ -2891,10 +2891,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>354900</v>
+        <v>63100</v>
       </c>
       <c r="E43" s="3">
-        <v>354900</v>
+        <v>63100</v>
       </c>
       <c r="F43" s="3">
         <v>32800</v>
@@ -3033,10 +3033,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>79100</v>
+        <v>370900</v>
       </c>
       <c r="E45" s="3">
-        <v>79100</v>
+        <v>370900</v>
       </c>
       <c r="F45" s="3">
         <v>161600</v>
@@ -3797,10 +3797,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>19300</v>
+        <v>19400</v>
       </c>
       <c r="E57" s="3">
-        <v>19300</v>
+        <v>19400</v>
       </c>
       <c r="F57" s="3">
         <v>12500</v>
@@ -3939,10 +3939,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="E59" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="F59" s="3">
         <v>12600</v>
@@ -5850,10 +5850,10 @@
         <v>-3100</v>
       </c>
       <c r="F89" s="3">
-        <v>-5100</v>
+        <v>-9800</v>
       </c>
       <c r="G89" s="3">
-        <v>-5100</v>
+        <v>-9800</v>
       </c>
       <c r="H89" s="3">
         <v>5800</v>
@@ -6685,10 +6685,10 @@
         <v>4200</v>
       </c>
       <c r="F102" s="3">
-        <v>-4600</v>
+        <v>-9300</v>
       </c>
       <c r="G102" s="3">
-        <v>-4600</v>
+        <v>-9300</v>
       </c>
       <c r="H102" s="3">
         <v>14600</v>
